--- a/data/herbicide_records.xlsx
+++ b/data/herbicide_records.xlsx
@@ -1,37 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Crop Type</t>
+  </si>
+  <si>
+    <t>Applied Area (ha)</t>
+  </si>
+  <si>
+    <t>MSMA</t>
+  </si>
+  <si>
+    <t>MCPA</t>
+  </si>
+  <si>
+    <t>Ametryn</t>
+  </si>
+  <si>
+    <t>Altrazine</t>
+  </si>
+  <si>
+    <t>Servian WP</t>
+  </si>
+  <si>
+    <t>Round-Up</t>
+  </si>
+  <si>
+    <t>Dual Magnum</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Garlon</t>
+  </si>
+  <si>
+    <t>Metolachlor</t>
+  </si>
+  <si>
+    <t>BB5</t>
+  </si>
+  <si>
+    <t>Mandays</t>
+  </si>
+  <si>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>Acetochlor</t>
+  </si>
+  <si>
+    <t>2525-01-05</t>
+  </si>
+  <si>
+    <t>2025-05-03</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>DG39000</t>
+  </si>
+  <si>
+    <t>DG01000</t>
+  </si>
+  <si>
+    <t>DG27004</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>2024/25</t>
+  </si>
+  <si>
+    <t>2025/26</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +164,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -179,7 +247,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -211,9 +279,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -245,6 +314,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -420,224 +490,343 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Crop Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Applied Area (ha)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MSMA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MCPA</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ametryn</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Altrazine</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Servian WP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Round-Up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Dual Magnum</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Garlon</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Acetylchro</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Metolachlor</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>BB5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Mandays</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Season</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Acetochlor</t>
-        </is>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2525-01-05</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DG39000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R579</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>9.347</v>
-      </c>
-      <c r="E2" t="n">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>9.3469999999999995</v>
+      </c>
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>10</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="P2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q2">
         <v>4</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2024/25</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DG01000</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MIX</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2025/26</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="P3">
+        <v>0.2</v>
+      </c>
+      <c r="Q3">
+        <v>18</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <v>6</v>
+      </c>
+      <c r="O4">
+        <v>6</v>
+      </c>
+      <c r="P4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0.2</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0.1</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>1.5</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>150</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>0.1</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>